--- a/artfynd/A 51519-2023 artfynd.xlsx
+++ b/artfynd/A 51519-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125702440</v>
+        <v>125702410</v>
       </c>
       <c r="B2" t="n">
         <v>78967</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501624</v>
+        <v>501615</v>
       </c>
       <c r="R2" t="n">
-        <v>6763057</v>
+        <v>6763119</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125702410</v>
+        <v>125702440</v>
       </c>
       <c r="B3" t="n">
         <v>78967</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501615</v>
+        <v>501624</v>
       </c>
       <c r="R3" t="n">
-        <v>6763119</v>
+        <v>6763057</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125702438</v>
+        <v>125702448</v>
       </c>
       <c r="B5" t="n">
         <v>78967</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501597</v>
+        <v>501581</v>
       </c>
       <c r="R5" t="n">
-        <v>6763076</v>
+        <v>6763110</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125702448</v>
+        <v>125702438</v>
       </c>
       <c r="B6" t="n">
         <v>78967</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>501581</v>
+        <v>501597</v>
       </c>
       <c r="R6" t="n">
-        <v>6763110</v>
+        <v>6763076</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125702434</v>
+        <v>125702450</v>
       </c>
       <c r="B11" t="n">
-        <v>78967</v>
+        <v>5176</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501619</v>
+        <v>501689</v>
       </c>
       <c r="R11" t="n">
-        <v>6763032</v>
+        <v>6763084</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125702450</v>
+        <v>125702434</v>
       </c>
       <c r="B12" t="n">
-        <v>5176</v>
+        <v>78967</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>501689</v>
+        <v>501619</v>
       </c>
       <c r="R12" t="n">
-        <v>6763084</v>
+        <v>6763032</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125702412</v>
+        <v>125702443</v>
       </c>
       <c r="B13" t="n">
         <v>78967</v>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501617</v>
+        <v>501546</v>
       </c>
       <c r="R13" t="n">
-        <v>6763121</v>
+        <v>6763056</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125702446</v>
+        <v>125702412</v>
       </c>
       <c r="B14" t="n">
         <v>78967</v>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501544</v>
+        <v>501617</v>
       </c>
       <c r="R14" t="n">
-        <v>6763085</v>
+        <v>6763121</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125702443</v>
+        <v>125702446</v>
       </c>
       <c r="B15" t="n">
         <v>78967</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>501546</v>
+        <v>501544</v>
       </c>
       <c r="R15" t="n">
-        <v>6763056</v>
+        <v>6763085</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>

--- a/artfynd/A 51519-2023 artfynd.xlsx
+++ b/artfynd/A 51519-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125702410</v>
       </c>
       <c r="B2" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125702440</v>
       </c>
       <c r="B3" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125702444</v>
       </c>
       <c r="B4" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125702448</v>
       </c>
       <c r="B5" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125702438</v>
       </c>
       <c r="B6" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125702415</v>
       </c>
       <c r="B7" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125702439</v>
       </c>
       <c r="B8" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125702437</v>
       </c>
       <c r="B9" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>125702434</v>
       </c>
       <c r="B12" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125702443</v>
+        <v>125702413</v>
       </c>
       <c r="B13" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501546</v>
+        <v>501604</v>
       </c>
       <c r="R13" t="n">
-        <v>6763056</v>
+        <v>6763123</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1842,7 +1842,7 @@
         <v>125702412</v>
       </c>
       <c r="B14" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>125702446</v>
       </c>
       <c r="B15" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125702413</v>
+        <v>125702443</v>
       </c>
       <c r="B16" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>501604</v>
+        <v>501546</v>
       </c>
       <c r="R16" t="n">
-        <v>6763123</v>
+        <v>6763056</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         <v>125702441</v>
       </c>
       <c r="B17" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>125702449</v>
       </c>
       <c r="B18" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>125702435</v>
       </c>
       <c r="B19" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>125702447</v>
       </c>
       <c r="B20" t="n">
-        <v>78967</v>
+        <v>78968</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 51519-2023 artfynd.xlsx
+++ b/artfynd/A 51519-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125702410</v>
+        <v>125702440</v>
       </c>
       <c r="B2" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501615</v>
+        <v>501624</v>
       </c>
       <c r="R2" t="n">
-        <v>6763119</v>
+        <v>6763057</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125702440</v>
+        <v>125702410</v>
       </c>
       <c r="B3" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501624</v>
+        <v>501615</v>
       </c>
       <c r="R3" t="n">
-        <v>6763057</v>
+        <v>6763119</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>125702444</v>
       </c>
       <c r="B4" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -966,10 +966,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125702448</v>
+        <v>125702438</v>
       </c>
       <c r="B5" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501581</v>
+        <v>501597</v>
       </c>
       <c r="R5" t="n">
-        <v>6763110</v>
+        <v>6763076</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,10 +1063,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125702438</v>
+        <v>125702448</v>
       </c>
       <c r="B6" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>501597</v>
+        <v>501581</v>
       </c>
       <c r="R6" t="n">
-        <v>6763076</v>
+        <v>6763110</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,7 +1163,7 @@
         <v>125702415</v>
       </c>
       <c r="B7" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125702439</v>
       </c>
       <c r="B8" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125702437</v>
       </c>
       <c r="B9" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1648,7 +1648,7 @@
         <v>125702434</v>
       </c>
       <c r="B12" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125702413</v>
+        <v>125702412</v>
       </c>
       <c r="B13" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501604</v>
+        <v>501617</v>
       </c>
       <c r="R13" t="n">
-        <v>6763123</v>
+        <v>6763121</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125702412</v>
+        <v>125702446</v>
       </c>
       <c r="B14" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501617</v>
+        <v>501544</v>
       </c>
       <c r="R14" t="n">
-        <v>6763121</v>
+        <v>6763085</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125702446</v>
+        <v>125702443</v>
       </c>
       <c r="B15" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>501544</v>
+        <v>501546</v>
       </c>
       <c r="R15" t="n">
-        <v>6763085</v>
+        <v>6763056</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125702443</v>
+        <v>125702413</v>
       </c>
       <c r="B16" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>501546</v>
+        <v>501604</v>
       </c>
       <c r="R16" t="n">
-        <v>6763056</v>
+        <v>6763123</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         <v>125702441</v>
       </c>
       <c r="B17" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>125702449</v>
       </c>
       <c r="B18" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>125702435</v>
       </c>
       <c r="B19" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>125702447</v>
       </c>
       <c r="B20" t="n">
-        <v>78968</v>
+        <v>78972</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 51519-2023 artfynd.xlsx
+++ b/artfynd/A 51519-2023 artfynd.xlsx
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125702438</v>
+        <v>125702448</v>
       </c>
       <c r="B5" t="n">
         <v>78972</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501597</v>
+        <v>501581</v>
       </c>
       <c r="R5" t="n">
-        <v>6763076</v>
+        <v>6763110</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125702448</v>
+        <v>125702438</v>
       </c>
       <c r="B6" t="n">
         <v>78972</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>501581</v>
+        <v>501597</v>
       </c>
       <c r="R6" t="n">
-        <v>6763110</v>
+        <v>6763076</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125702450</v>
+        <v>125702434</v>
       </c>
       <c r="B11" t="n">
-        <v>5176</v>
+        <v>78972</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501689</v>
+        <v>501619</v>
       </c>
       <c r="R11" t="n">
-        <v>6763084</v>
+        <v>6763032</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125702434</v>
+        <v>125702450</v>
       </c>
       <c r="B12" t="n">
-        <v>78972</v>
+        <v>5176</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>501619</v>
+        <v>501689</v>
       </c>
       <c r="R12" t="n">
-        <v>6763032</v>
+        <v>6763084</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 51519-2023 artfynd.xlsx
+++ b/artfynd/A 51519-2023 artfynd.xlsx
@@ -966,7 +966,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125702448</v>
+        <v>125702438</v>
       </c>
       <c r="B5" t="n">
         <v>78972</v>
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501581</v>
+        <v>501597</v>
       </c>
       <c r="R5" t="n">
-        <v>6763110</v>
+        <v>6763076</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,7 +1063,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125702438</v>
+        <v>125702448</v>
       </c>
       <c r="B6" t="n">
         <v>78972</v>
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>501597</v>
+        <v>501581</v>
       </c>
       <c r="R6" t="n">
-        <v>6763076</v>
+        <v>6763110</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>

--- a/artfynd/A 51519-2023 artfynd.xlsx
+++ b/artfynd/A 51519-2023 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>125702440</v>
       </c>
       <c r="B2" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>125702410</v>
       </c>
       <c r="B3" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>125702444</v>
       </c>
       <c r="B4" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125702438</v>
       </c>
       <c r="B5" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125702448</v>
       </c>
       <c r="B6" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125702415</v>
       </c>
       <c r="B7" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125702439</v>
       </c>
       <c r="B8" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125702437</v>
       </c>
       <c r="B9" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>125702434</v>
       </c>
       <c r="B11" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1745,7 +1745,7 @@
         <v>125702412</v>
       </c>
       <c r="B13" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1842,7 +1842,7 @@
         <v>125702446</v>
       </c>
       <c r="B14" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1939,7 +1939,7 @@
         <v>125702443</v>
       </c>
       <c r="B15" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2036,7 +2036,7 @@
         <v>125702413</v>
       </c>
       <c r="B16" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2133,7 +2133,7 @@
         <v>125702441</v>
       </c>
       <c r="B17" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>125702449</v>
       </c>
       <c r="B18" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2327,7 +2327,7 @@
         <v>125702435</v>
       </c>
       <c r="B19" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2424,7 +2424,7 @@
         <v>125702447</v>
       </c>
       <c r="B20" t="n">
-        <v>78972</v>
+        <v>78973</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>

--- a/artfynd/A 51519-2023 artfynd.xlsx
+++ b/artfynd/A 51519-2023 artfynd.xlsx
@@ -2130,7 +2130,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125702441</v>
+        <v>125702449</v>
       </c>
       <c r="B17" t="n">
         <v>78973</v>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>501618</v>
+        <v>501589</v>
       </c>
       <c r="R17" t="n">
-        <v>6763083</v>
+        <v>6763112</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125702449</v>
+        <v>125702441</v>
       </c>
       <c r="B18" t="n">
         <v>78973</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>501589</v>
+        <v>501618</v>
       </c>
       <c r="R18" t="n">
-        <v>6763112</v>
+        <v>6763083</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 51519-2023 artfynd.xlsx
+++ b/artfynd/A 51519-2023 artfynd.xlsx
@@ -2130,7 +2130,7 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125702449</v>
+        <v>125702441</v>
       </c>
       <c r="B17" t="n">
         <v>78973</v>
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>501589</v>
+        <v>501618</v>
       </c>
       <c r="R17" t="n">
-        <v>6763112</v>
+        <v>6763083</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,7 +2227,7 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125702441</v>
+        <v>125702449</v>
       </c>
       <c r="B18" t="n">
         <v>78973</v>
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>501618</v>
+        <v>501589</v>
       </c>
       <c r="R18" t="n">
-        <v>6763083</v>
+        <v>6763112</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>

--- a/artfynd/A 51519-2023 artfynd.xlsx
+++ b/artfynd/A 51519-2023 artfynd.xlsx
@@ -675,7 +675,7 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125702440</v>
+        <v>125702410</v>
       </c>
       <c r="B2" t="n">
         <v>78973</v>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501624</v>
+        <v>501615</v>
       </c>
       <c r="R2" t="n">
-        <v>6763057</v>
+        <v>6763119</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,7 +772,7 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125702410</v>
+        <v>125702440</v>
       </c>
       <c r="B3" t="n">
         <v>78973</v>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501615</v>
+        <v>501624</v>
       </c>
       <c r="R3" t="n">
-        <v>6763119</v>
+        <v>6763057</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125702434</v>
+        <v>125702450</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>5176</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501619</v>
+        <v>501689</v>
       </c>
       <c r="R11" t="n">
-        <v>6763032</v>
+        <v>6763084</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125702450</v>
+        <v>125702434</v>
       </c>
       <c r="B12" t="n">
-        <v>5176</v>
+        <v>78973</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>501689</v>
+        <v>501619</v>
       </c>
       <c r="R12" t="n">
-        <v>6763084</v>
+        <v>6763032</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,7 +1742,7 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125702412</v>
+        <v>125702446</v>
       </c>
       <c r="B13" t="n">
         <v>78973</v>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501617</v>
+        <v>501544</v>
       </c>
       <c r="R13" t="n">
-        <v>6763121</v>
+        <v>6763085</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,7 +1839,7 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125702446</v>
+        <v>125702413</v>
       </c>
       <c r="B14" t="n">
         <v>78973</v>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501544</v>
+        <v>501604</v>
       </c>
       <c r="R14" t="n">
-        <v>6763085</v>
+        <v>6763123</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,7 +1936,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125702443</v>
+        <v>125702412</v>
       </c>
       <c r="B15" t="n">
         <v>78973</v>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>501546</v>
+        <v>501617</v>
       </c>
       <c r="R15" t="n">
-        <v>6763056</v>
+        <v>6763121</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,7 +2033,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125702413</v>
+        <v>125702443</v>
       </c>
       <c r="B16" t="n">
         <v>78973</v>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>501604</v>
+        <v>501546</v>
       </c>
       <c r="R16" t="n">
-        <v>6763123</v>
+        <v>6763056</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>

--- a/artfynd/A 51519-2023 artfynd.xlsx
+++ b/artfynd/A 51519-2023 artfynd.xlsx
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125702450</v>
+        <v>125702434</v>
       </c>
       <c r="B11" t="n">
-        <v>5176</v>
+        <v>78973</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501689</v>
+        <v>501619</v>
       </c>
       <c r="R11" t="n">
-        <v>6763084</v>
+        <v>6763032</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125702434</v>
+        <v>125702450</v>
       </c>
       <c r="B12" t="n">
-        <v>78973</v>
+        <v>5176</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>501619</v>
+        <v>501689</v>
       </c>
       <c r="R12" t="n">
-        <v>6763032</v>
+        <v>6763084</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -2324,7 +2324,7 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125702435</v>
+        <v>125702447</v>
       </c>
       <c r="B19" t="n">
         <v>78973</v>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>501610</v>
+        <v>501555</v>
       </c>
       <c r="R19" t="n">
-        <v>6763049</v>
+        <v>6763085</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,7 +2421,7 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125702447</v>
+        <v>125702435</v>
       </c>
       <c r="B20" t="n">
         <v>78973</v>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>501555</v>
+        <v>501610</v>
       </c>
       <c r="R20" t="n">
-        <v>6763085</v>
+        <v>6763049</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 51519-2023 artfynd.xlsx
+++ b/artfynd/A 51519-2023 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125702410</v>
+        <v>125702440</v>
       </c>
       <c r="B2" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501615</v>
+        <v>501624</v>
       </c>
       <c r="R2" t="n">
-        <v>6763119</v>
+        <v>6763057</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -772,10 +772,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>125702440</v>
+        <v>125702410</v>
       </c>
       <c r="B3" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>501624</v>
+        <v>501615</v>
       </c>
       <c r="R3" t="n">
-        <v>6763057</v>
+        <v>6763119</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -872,7 +872,7 @@
         <v>125702444</v>
       </c>
       <c r="B4" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -969,7 +969,7 @@
         <v>125702438</v>
       </c>
       <c r="B5" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,7 +1066,7 @@
         <v>125702448</v>
       </c>
       <c r="B6" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1163,7 +1163,7 @@
         <v>125702415</v>
       </c>
       <c r="B7" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1260,7 +1260,7 @@
         <v>125702439</v>
       </c>
       <c r="B8" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1357,7 +1357,7 @@
         <v>125702437</v>
       </c>
       <c r="B9" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1551,7 +1551,7 @@
         <v>125702434</v>
       </c>
       <c r="B11" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1742,10 +1742,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125702446</v>
+        <v>125702412</v>
       </c>
       <c r="B13" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501544</v>
+        <v>501617</v>
       </c>
       <c r="R13" t="n">
-        <v>6763085</v>
+        <v>6763121</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,10 +1839,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125702413</v>
+        <v>125702446</v>
       </c>
       <c r="B14" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501604</v>
+        <v>501544</v>
       </c>
       <c r="R14" t="n">
-        <v>6763123</v>
+        <v>6763085</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,10 +1936,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125702412</v>
+        <v>125702443</v>
       </c>
       <c r="B15" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -1971,10 +1971,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>501617</v>
+        <v>501546</v>
       </c>
       <c r="R15" t="n">
-        <v>6763121</v>
+        <v>6763056</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2033,10 +2033,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125702443</v>
+        <v>125702413</v>
       </c>
       <c r="B16" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>501546</v>
+        <v>501604</v>
       </c>
       <c r="R16" t="n">
-        <v>6763056</v>
+        <v>6763123</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2133,7 +2133,7 @@
         <v>125702441</v>
       </c>
       <c r="B17" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2230,7 +2230,7 @@
         <v>125702449</v>
       </c>
       <c r="B18" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2324,10 +2324,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125702447</v>
+        <v>125702435</v>
       </c>
       <c r="B19" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>501555</v>
+        <v>501610</v>
       </c>
       <c r="R19" t="n">
-        <v>6763085</v>
+        <v>6763049</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,10 +2421,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125702435</v>
+        <v>125702447</v>
       </c>
       <c r="B20" t="n">
-        <v>78973</v>
+        <v>78977</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>501610</v>
+        <v>501555</v>
       </c>
       <c r="R20" t="n">
-        <v>6763049</v>
+        <v>6763085</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>

--- a/artfynd/A 51519-2023 artfynd.xlsx
+++ b/artfynd/A 51519-2023 artfynd.xlsx
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125702434</v>
+        <v>125702450</v>
       </c>
       <c r="B11" t="n">
-        <v>78977</v>
+        <v>5176</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6425</v>
+        <v>100526</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501619</v>
+        <v>501689</v>
       </c>
       <c r="R11" t="n">
-        <v>6763032</v>
+        <v>6763084</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,32 +1645,32 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125702450</v>
+        <v>125702434</v>
       </c>
       <c r="B12" t="n">
-        <v>5176</v>
+        <v>78977</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>501689</v>
+        <v>501619</v>
       </c>
       <c r="R12" t="n">
-        <v>6763084</v>
+        <v>6763032</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>

--- a/artfynd/A 51519-2023 artfynd.xlsx
+++ b/artfynd/A 51519-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY20"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,14 +675,14 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>125702440</v>
+        <v>125702407</v>
       </c>
       <c r="B2" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>501624</v>
+        <v>501501</v>
       </c>
       <c r="R2" t="n">
-        <v>6763057</v>
+        <v>6762987</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -775,11 +775,11 @@
         <v>125702410</v>
       </c>
       <c r="B3" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -869,14 +869,14 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>125702444</v>
+        <v>125702412</v>
       </c>
       <c r="B4" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E4" t="n">
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>501502</v>
+        <v>501617</v>
       </c>
       <c r="R4" t="n">
-        <v>6763013</v>
+        <v>6763121</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -966,14 +966,14 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>125702438</v>
+        <v>125702413</v>
       </c>
       <c r="B5" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E5" t="n">
@@ -1001,10 +1001,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>501597</v>
+        <v>501604</v>
       </c>
       <c r="R5" t="n">
-        <v>6763076</v>
+        <v>6763123</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1063,14 +1063,14 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>125702448</v>
+        <v>125702414</v>
       </c>
       <c r="B6" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E6" t="n">
@@ -1098,10 +1098,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>501581</v>
+        <v>501606</v>
       </c>
       <c r="R6" t="n">
-        <v>6763110</v>
+        <v>6763153</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1163,11 +1163,11 @@
         <v>125702415</v>
       </c>
       <c r="B7" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E7" t="n">
@@ -1257,14 +1257,14 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>125702439</v>
+        <v>125702434</v>
       </c>
       <c r="B8" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E8" t="n">
@@ -1292,10 +1292,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>501639</v>
+        <v>501619</v>
       </c>
       <c r="R8" t="n">
-        <v>6763056</v>
+        <v>6763032</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1354,14 +1354,14 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>125702437</v>
+        <v>125702435</v>
       </c>
       <c r="B9" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
@@ -1389,10 +1389,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>501603</v>
+        <v>501610</v>
       </c>
       <c r="R9" t="n">
-        <v>6763062</v>
+        <v>6763049</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1451,32 +1451,32 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>125702451</v>
+        <v>125702437</v>
       </c>
       <c r="B10" t="n">
-        <v>5176</v>
+        <v>79327</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
@@ -1486,10 +1486,10 @@
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>501686</v>
+        <v>501603</v>
       </c>
       <c r="R10" t="n">
-        <v>6763073</v>
+        <v>6763062</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1548,32 +1548,32 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>125702450</v>
+        <v>125702438</v>
       </c>
       <c r="B11" t="n">
-        <v>5176</v>
+        <v>79327</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>100526</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1583,10 +1583,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>501689</v>
+        <v>501597</v>
       </c>
       <c r="R11" t="n">
-        <v>6763084</v>
+        <v>6763076</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1645,14 +1645,14 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>125702434</v>
+        <v>125702439</v>
       </c>
       <c r="B12" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E12" t="n">
@@ -1680,10 +1680,10 @@
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>501619</v>
+        <v>501639</v>
       </c>
       <c r="R12" t="n">
-        <v>6763032</v>
+        <v>6763056</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1742,14 +1742,14 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>125702412</v>
+        <v>125702440</v>
       </c>
       <c r="B13" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
@@ -1777,10 +1777,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>501617</v>
+        <v>501624</v>
       </c>
       <c r="R13" t="n">
-        <v>6763121</v>
+        <v>6763057</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1839,14 +1839,14 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>125702446</v>
+        <v>125702441</v>
       </c>
       <c r="B14" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
@@ -1874,10 +1874,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>501544</v>
+        <v>501618</v>
       </c>
       <c r="R14" t="n">
-        <v>6763085</v>
+        <v>6763083</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -1936,14 +1936,14 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>125702443</v>
+        <v>125702442</v>
       </c>
       <c r="B15" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
@@ -2033,14 +2033,14 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>125702413</v>
+        <v>125702444</v>
       </c>
       <c r="B16" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
@@ -2068,10 +2068,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>501604</v>
+        <v>501502</v>
       </c>
       <c r="R16" t="n">
-        <v>6763123</v>
+        <v>6763013</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2130,14 +2130,14 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>125702441</v>
+        <v>125702446</v>
       </c>
       <c r="B17" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
@@ -2165,10 +2165,10 @@
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>501618</v>
+        <v>501544</v>
       </c>
       <c r="R17" t="n">
-        <v>6763083</v>
+        <v>6763085</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2227,14 +2227,14 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>125702449</v>
+        <v>125702447</v>
       </c>
       <c r="B18" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
@@ -2262,10 +2262,10 @@
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>501589</v>
+        <v>501555</v>
       </c>
       <c r="R18" t="n">
-        <v>6763112</v>
+        <v>6763085</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2324,14 +2324,14 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>125702435</v>
+        <v>125702448</v>
       </c>
       <c r="B19" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
@@ -2359,10 +2359,10 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>501610</v>
+        <v>501581</v>
       </c>
       <c r="R19" t="n">
-        <v>6763049</v>
+        <v>6763110</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2421,14 +2421,14 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>125702447</v>
+        <v>125702449</v>
       </c>
       <c r="B20" t="n">
-        <v>78977</v>
+        <v>79327</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E20" t="n">
@@ -2456,10 +2456,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>501555</v>
+        <v>501589</v>
       </c>
       <c r="R20" t="n">
-        <v>6763085</v>
+        <v>6763112</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2515,6 +2515,297 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>125702452</v>
+      </c>
+      <c r="B21" t="n">
+        <v>79327</v>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>501629</v>
+      </c>
+      <c r="R21" t="n">
+        <v>6763012</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>125702450</v>
+      </c>
+      <c r="B22" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>501689</v>
+      </c>
+      <c r="R22" t="n">
+        <v>6763084</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>125702451</v>
+      </c>
+      <c r="B23" t="n">
+        <v>5179</v>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>100526</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Bronshjon</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Callidium coriaceum</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>Paykull, 1800</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Larsbodarna, Dlr</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>501686</v>
+      </c>
+      <c r="R23" t="n">
+        <v>6763073</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Dalarna</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Rättvik</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2025-03-22</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Anna-Britt Olsson</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 51519-2023 artfynd.xlsx
+++ b/artfynd/A 51519-2023 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AZ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125702407</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125702410</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125702412</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125702413</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125702414</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125702415</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125702434</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,6 +1488,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125702435</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1545,6 +1590,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125702437</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1642,6 +1692,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125702438</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1739,6 +1794,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125702439</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1836,6 +1896,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125702440</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -1933,6 +1998,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125702441</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2030,6 +2100,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125702442</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2127,6 +2202,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125702444</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2224,6 +2304,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125702446</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2321,6 +2406,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125702447</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2418,6 +2508,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125702448</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2515,6 +2610,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125702449</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2612,6 +2712,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125702452</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2709,6 +2814,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125702450</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2806,8 +2916,37 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125702451</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>